--- a/Excel_na_zal.xlsx
+++ b/Excel_na_zal.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29711"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KN\Desktop\Maciej L\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B4ECA0-B7D6-4468-A5B1-A75953165A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -131,14 +130,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.0000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +166,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -229,13 +236,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -245,6 +245,13 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -525,9 +532,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK1048576"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -541,11 +548,11 @@
     <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" t="s">
         <v>1</v>
       </c>
@@ -555,10 +562,10 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="11"/>
+      <c r="K1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="21"/>
       <c r="M1" t="s">
         <v>1</v>
       </c>
@@ -569,11 +576,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="11"/>
+      <c r="B2" s="21"/>
       <c r="C2">
         <v>10</v>
       </c>
@@ -591,10 +598,10 @@
         <f>IF(E2=E5,RADIANS(C2+D2/60),IF(AND(E2="S",E5="N"),-RADIANS(C2+D2/60),RADIANS(C2+D2/60)))</f>
         <v>0.17453292519943295</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="11"/>
+      <c r="L2" s="21"/>
       <c r="M2">
         <v>40</v>
       </c>
@@ -613,11 +620,11 @@
         <v>0.69813170079773179</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="21"/>
       <c r="C3">
         <v>10</v>
       </c>
@@ -635,10 +642,10 @@
         <f t="shared" ref="G3:G6" si="1">RADIANS(C3+D3/60)</f>
         <v>0.17453292519943295</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="21"/>
       <c r="M3">
         <v>10</v>
       </c>
@@ -657,7 +664,7 @@
         <v>0.17453292519943295</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -667,11 +674,11 @@
       </c>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="21"/>
       <c r="C5">
         <v>80</v>
       </c>
@@ -689,10 +696,10 @@
         <f>IF(E2=E5,RADIANS(C5+D5/60),IF(AND(E2="S",E5="N"),RADIANS(C5+D5/60),-RADIANS(C5+D5/60)))</f>
         <v>1.3962634015954636</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="21"/>
       <c r="M5">
         <v>30</v>
       </c>
@@ -711,11 +718,11 @@
         <v>0.52359877559829882</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="21"/>
       <c r="C6">
         <v>20</v>
       </c>
@@ -733,10 +740,10 @@
         <f t="shared" si="1"/>
         <v>0.3490658503988659</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="21"/>
       <c r="M6">
         <v>100</v>
       </c>
@@ -755,11 +762,11 @@
         <v>1.7453292519943295</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="4">
         <f>DEGREES(ACOS(SIN(G2)*SIN(G5)+COS(G2)*COS(G5)*COS(G6-G3)))*60</f>
         <v>4209.4997892631818</v>
@@ -768,10 +775,10 @@
         <f>ACOS(SIN(G2)*SIN(G5)+COS(G2)*COS(G5)*COS(G6-G3))</f>
         <v>1.2244938530774996</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="21"/>
       <c r="M8" s="4">
         <f>DEGREES(ACOS(SIN(Q2)*SIN(Q5)+COS(Q2)*COS(Q5)*COS(Q6-Q3)))*60</f>
         <v>4275.1657649377494</v>
@@ -781,11 +788,11 @@
         <v>1.2435953111117615</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="4">
         <f>IF(D9&lt;0,D9+360,D9)</f>
         <v>358.16296785523269</v>
@@ -798,10 +805,10 @@
         <f>RADIANS(C9)</f>
         <v>6.2511230477884236</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="21"/>
       <c r="M9" s="4">
         <f>IF(N9&lt;0,N9+360,N9)</f>
         <v>66.141345201541355</v>
@@ -815,25 +822,25 @@
         <v>1.154384245465049</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="4">
         <f>IF(DEGREES(ASIN(SIN(G3-G6))*COS(G2)*_xlfn.CSC(D8))&lt;0,DEGREES(ASIN(SIN(G3-G6))*COS(G2)*_xlfn.CSC(D8))+360,DEGREES(ASIN(SIN(G3-G6))*COS(G2)*_xlfn.CSC(D8))+180)</f>
         <v>349.53038500431808</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="21"/>
       <c r="M10" s="4">
         <f>DEGREES(ASIN(SIN(Q3-Q6)*COS(Q2)*_xlfn.CSC(N8)))+180</f>
         <v>126.00521481878653</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
         <f>IF(DEGREES(ACOS(C12))&gt;90,180-DEGREES(ACOS(C12)),DEGREES(ACOS(C12)))</f>
         <v>88.190885851442943</v>
@@ -851,7 +858,7 @@
         <v>0.70058293593547727</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>ROUNDDOWN(B12,0)</f>
         <v>88</v>
@@ -876,7 +883,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <f>DEGREES(_xlfn.ACOT(C14))-90</f>
         <v>0.31910333834673565</v>
@@ -886,11 +893,11 @@
         <v>-5.5694614933767071E-3</v>
       </c>
     </row>
-    <row r="18" spans="11:17">
-      <c r="K18" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11"/>
+    <row r="18" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K18" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="21"/>
       <c r="M18" t="s">
         <v>1</v>
       </c>
@@ -901,11 +908,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="11:17">
-      <c r="K19" s="11" t="s">
+    <row r="19" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K19" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L19" s="11"/>
+      <c r="L19" s="21"/>
       <c r="M19">
         <v>50</v>
       </c>
@@ -924,11 +931,11 @@
         <v>0.87266462599716477</v>
       </c>
     </row>
-    <row r="20" spans="11:17">
-      <c r="K20" s="11" t="s">
+    <row r="20" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K20" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="11"/>
+      <c r="L20" s="21"/>
       <c r="M20">
         <v>150</v>
       </c>
@@ -947,17 +954,17 @@
         <v>2.6179938779914944</v>
       </c>
     </row>
-    <row r="21" spans="11:17">
+    <row r="21" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="11:17">
-      <c r="K22" s="11" t="s">
+    <row r="22" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K22" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="11"/>
+      <c r="L22" s="21"/>
       <c r="M22">
         <v>45</v>
       </c>
@@ -976,11 +983,11 @@
         <v>0.78539816339744828</v>
       </c>
     </row>
-    <row r="23" spans="11:17">
-      <c r="K23" s="11" t="s">
+    <row r="23" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K23" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="11"/>
+      <c r="L23" s="21"/>
       <c r="M23">
         <v>140</v>
       </c>
@@ -999,11 +1006,11 @@
         <v>2.4434609527920612</v>
       </c>
     </row>
-    <row r="25" spans="11:17">
-      <c r="K25" s="11" t="s">
+    <row r="25" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K25" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="11"/>
+      <c r="L25" s="21"/>
       <c r="M25" s="4">
         <f>DEGREES(ACOS(SIN(Q19)*SIN(Q22)+COS(Q19)*COS(Q22)*COS(Q23-Q20)))*60</f>
         <v>503.59523959029184</v>
@@ -1013,11 +1020,11 @@
         <v>0.14648991713700488</v>
       </c>
     </row>
-    <row r="26" spans="11:17">
-      <c r="K26" s="11" t="s">
+    <row r="26" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K26" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="L26" s="11"/>
+      <c r="L26" s="21"/>
       <c r="M26" s="4">
         <f>IF(N26&lt;0,N26+360,N26)</f>
         <v>302.73240720961201</v>
@@ -1031,17 +1038,17 @@
         <v>5.283677258295949</v>
       </c>
     </row>
-    <row r="27" spans="11:17">
-      <c r="K27" s="11" t="s">
+    <row r="27" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K27" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="11"/>
+      <c r="L27" s="21"/>
       <c r="M27" s="4">
         <f>DEGREES(ASIN(SIN(Q20-Q23)*COS(Q19)*_xlfn.CSC(N25)))+180</f>
         <v>229.87925979145729</v>
       </c>
     </row>
-    <row r="29" spans="11:17">
+    <row r="29" spans="11:17" x14ac:dyDescent="0.25">
       <c r="L29" s="7">
         <f>IF(DEGREES(ACOS(M29))&gt;90,180-DEGREES(ACOS(M29)),DEGREES(ACOS(M29)))</f>
         <v>57.267592790387496</v>
@@ -1051,7 +1058,7 @@
         <v>-0.54071620306093893</v>
       </c>
     </row>
-    <row r="30" spans="11:17">
+    <row r="30" spans="11:17" x14ac:dyDescent="0.25">
       <c r="K30" s="5">
         <f>ROUNDDOWN(L29,0)</f>
         <v>57</v>
@@ -1065,11 +1072,11 @@
         <v>S</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
-      <c r="A86" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B86" s="12"/>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A86" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="20"/>
       <c r="C86" s="2" t="s">
         <v>1</v>
       </c>
@@ -1080,15 +1087,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
-      <c r="A87" s="11" t="s">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A87" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B87" s="11"/>
-      <c r="C87" s="14">
-        <v>55</v>
-      </c>
-      <c r="D87" s="14">
+      <c r="B87" s="21"/>
+      <c r="C87" s="11">
+        <v>60</v>
+      </c>
+      <c r="D87" s="11">
         <v>0</v>
       </c>
       <c r="E87" t="s">
@@ -1096,25 +1103,25 @@
       </c>
       <c r="F87">
         <f>C87+D87/60</f>
-        <v>55</v>
-      </c>
-      <c r="G87" s="16">
+        <v>60</v>
+      </c>
+      <c r="G87" s="13">
         <f t="shared" ref="G87:G90" si="10">RADIANS(C87+D87/60)</f>
-        <v>0.95993108859688125</v>
+        <v>1.0471975511965976</v>
       </c>
       <c r="S87" s="10"/>
       <c r="T87" s="5"/>
       <c r="U87" s="4"/>
     </row>
-    <row r="88" spans="1:21">
-      <c r="A88" s="11" t="s">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A88" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B88" s="11"/>
-      <c r="C88" s="14">
-        <v>0</v>
-      </c>
-      <c r="D88" s="14">
+      <c r="B88" s="21"/>
+      <c r="C88" s="11">
+        <v>-70</v>
+      </c>
+      <c r="D88" s="11">
         <v>0</v>
       </c>
       <c r="E88" t="s">
@@ -1122,34 +1129,34 @@
       </c>
       <c r="F88">
         <f t="shared" ref="F88" si="11">C88+D88/60</f>
-        <v>0</v>
-      </c>
-      <c r="G88" s="16">
+        <v>-70</v>
+      </c>
+      <c r="G88" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-1.2217304763960306</v>
       </c>
       <c r="S88" s="10"/>
       <c r="T88" s="5"/>
       <c r="U88" s="4"/>
     </row>
-    <row r="89" spans="1:21">
-      <c r="A89" s="12" t="s">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A89" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="12"/>
+      <c r="B89" s="20"/>
       <c r="S89" s="10"/>
       <c r="T89" s="5"/>
       <c r="U89" s="4"/>
     </row>
-    <row r="90" spans="1:21">
-      <c r="A90" s="11" t="s">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A90" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B90" s="11"/>
-      <c r="C90" s="14">
-        <v>60</v>
-      </c>
-      <c r="D90" s="14">
+      <c r="B90" s="21"/>
+      <c r="C90" s="11">
+        <v>55</v>
+      </c>
+      <c r="D90" s="11">
         <v>0</v>
       </c>
       <c r="E90" t="s">
@@ -1157,48 +1164,48 @@
       </c>
       <c r="F90">
         <f t="shared" ref="F90:F91" si="12">C90+D90/60</f>
-        <v>60</v>
-      </c>
-      <c r="G90" s="16">
+        <v>55</v>
+      </c>
+      <c r="G90" s="13">
         <f t="shared" si="10"/>
-        <v>1.0471975511965976</v>
+        <v>0.95993108859688125</v>
       </c>
       <c r="S90" s="10"/>
       <c r="T90" s="5"/>
       <c r="U90" s="4"/>
     </row>
-    <row r="91" spans="1:21">
-      <c r="A91" s="11" t="s">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="14">
-        <v>60</v>
-      </c>
-      <c r="D91" s="15">
+      <c r="B91" s="21"/>
+      <c r="C91" s="11">
+        <v>-10</v>
+      </c>
+      <c r="D91" s="12">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F91">
         <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-      <c r="G91" s="16">
+        <v>-10</v>
+      </c>
+      <c r="G91" s="13">
         <f>RADIANS(C91+D91/60)</f>
-        <v>1.0471975511965976</v>
+        <v>-0.17453292519943295</v>
       </c>
       <c r="S91" s="10"/>
       <c r="T91" s="5"/>
       <c r="U91" s="4"/>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S92" s="10"/>
       <c r="T92" s="5"/>
       <c r="U92" s="4"/>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C93" s="2" t="s">
         <v>13</v>
       </c>
@@ -1206,12 +1213,12 @@
       <c r="T93" s="5"/>
       <c r="U93" s="4"/>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B94" s="4">
         <f>ACOS(SIN(G87)*SIN(G90)+COS(G87)*COS(G90)*COS(G91-G88))</f>
         <v>0.54947160375159321</v>
       </c>
-      <c r="C94" s="17">
+      <c r="C94" s="14">
         <f>DEGREES(ACOS(SIN(G87)*SIN(G90)+COS(G87)*COS(G90)*COS(G91-G88)))*60</f>
         <v>1888.9442314350613</v>
       </c>
@@ -1219,31 +1226,31 @@
       <c r="T94" s="5"/>
       <c r="U94" s="4"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="18">
-        <f>DEGREES(ASIN(SIN(G91-G88)*COS(G90)/SIN(B94)))</f>
-        <v>56.011551499089663</v>
+      <c r="C95" s="15">
+        <f>DEGREES(ASIN(SIN((G91-G88))*COS(G90)/SIN(B94)))</f>
+        <v>72.019594959291112</v>
       </c>
       <c r="S95" s="10"/>
       <c r="T95" s="5"/>
       <c r="U95" s="4"/>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="19">
-        <f>180-DEGREES(ASIN(SIN(G91-G88)*COS(G87)/SIN(B94)))</f>
-        <v>107.98040504070889</v>
+      <c r="C96" s="16">
+        <f>180-DEGREES(ASIN(SIN((G91-G88))*COS(G87)/SIN(B94)))</f>
+        <v>123.98844850091034</v>
       </c>
       <c r="S96" s="10"/>
       <c r="T96" s="5"/>
       <c r="U96" s="4"/>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C97" s="2" t="s">
         <v>16</v>
       </c>
@@ -1253,79 +1260,82 @@
       <c r="E97" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13">
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22">
         <f>(F87-F90)*60</f>
-        <v>-300</v>
-      </c>
-      <c r="J97" s="13"/>
-      <c r="K97" s="13"/>
+        <v>300</v>
+      </c>
+      <c r="J97" s="22"/>
+      <c r="K97" s="22"/>
+      <c r="L97" s="22"/>
       <c r="S97" s="10"/>
       <c r="T97" s="5"/>
       <c r="U97" s="4"/>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="17">
+      <c r="C98" s="14">
         <f>DEGREES(ACOS(ABS(COS(G87)*SIN(RADIANS(C95)))))</f>
         <v>61.602809708243164</v>
       </c>
-      <c r="D98" s="17">
+      <c r="D98" s="14">
         <f>ROUNDDOWN(C98,0)</f>
         <v>61</v>
       </c>
-      <c r="E98" s="20">
+      <c r="E98" s="17">
         <f>(C98-D98)*60</f>
         <v>36.168582494589856</v>
       </c>
-      <c r="G98" s="13">
-        <f>(C88-C91)*60</f>
-        <v>-3600</v>
-      </c>
-      <c r="H98" s="13">
+      <c r="G98" s="22">
+        <f>-(C88-C91)*60</f>
+        <v>3600</v>
+      </c>
+      <c r="H98" s="22">
         <f>COS((G90+G87)/2)</f>
         <v>0.53729960834682389</v>
       </c>
-      <c r="I98" s="13">
+      <c r="I98" s="22">
         <f>G98*H98</f>
-        <v>-1934.278590048566</v>
-      </c>
-      <c r="J98" s="13"/>
-      <c r="K98" s="13">
+        <v>1934.278590048566</v>
+      </c>
+      <c r="J98" s="22"/>
+      <c r="K98" s="22">
         <f>ACOS((I98/C101))</f>
-        <v>2.98772203775885</v>
-      </c>
+        <v>0.15387061583094308</v>
+      </c>
+      <c r="L98" s="22"/>
       <c r="W98" s="4"/>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C99" s="17">
-        <f>DEGREES(_xlfn.ACOT(SIN(G87)*TAN(RADIANS(C95))))</f>
-        <v>39.456594076789116</v>
-      </c>
-      <c r="D99" s="17">
+      <c r="C99" s="14">
+        <f>C88+DEGREES(_xlfn.ACOT(SIN(G87)*TAN(RADIANS(C95))))</f>
+        <v>-49.456594076789209</v>
+      </c>
+      <c r="D99" s="14">
         <f>ROUNDDOWN(C99,0)</f>
-        <v>39</v>
-      </c>
-      <c r="E99" s="20">
+        <v>-49</v>
+      </c>
+      <c r="E99" s="17">
         <f>(C99-D99)*60</f>
-        <v>27.395644607346981</v>
-      </c>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13">
+        <v>-27.395644607352523</v>
+      </c>
+      <c r="G99" s="22"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="22">
         <f>(I98/I97)</f>
         <v>6.4475953001618871</v>
       </c>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
-    </row>
-    <row r="100" spans="1:23">
+      <c r="J99" s="22"/>
+      <c r="K99" s="22"/>
+      <c r="L99" s="22"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C100" s="2" t="s">
         <v>21</v>
       </c>
@@ -1333,26 +1343,94 @@
       <c r="E100" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="101" spans="1:23">
-      <c r="C101" s="20">
+      <c r="G100" s="22"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="22"/>
+      <c r="J100" s="22"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="P100">
+        <f>(C104-C107)*60</f>
+        <v>-96.103897358528059</v>
+      </c>
+      <c r="T100">
+        <f>(C107-C110)*60</f>
+        <v>85.844192023850638</v>
+      </c>
+      <c r="X100">
+        <f>(C110-C113)*60</f>
+        <v>310.2597053346791</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C101" s="17">
         <f>DEGREES((((G91-G88)*COS((G87+G90)/2))^2+(G90-G87)^2)^(1/2))*60</f>
         <v>1957.4048288282797</v>
       </c>
-      <c r="D101" s="21">
+      <c r="D101" s="18">
         <f>C101/60</f>
         <v>32.62341381380466</v>
       </c>
-      <c r="E101" s="18">
+      <c r="E101" s="15">
         <f>180-DEGREES(ATAN(I99))</f>
         <v>98.816136878191983</v>
       </c>
-    </row>
-    <row r="103" spans="1:23">
-      <c r="A103" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B103" s="12"/>
+      <c r="N101">
+        <f>(C105-C108)*60</f>
+        <v>-1200</v>
+      </c>
+      <c r="O101">
+        <f>COS((H107+H104)/2)</f>
+        <v>0.48784646813208676</v>
+      </c>
+      <c r="P101">
+        <f>N101*O101</f>
+        <v>-585.41576175850412</v>
+      </c>
+      <c r="R101">
+        <f>(C105-C108)*60</f>
+        <v>-1200</v>
+      </c>
+      <c r="S101">
+        <f>COS((H110+H107)/2)</f>
+        <v>0.48654332822882917</v>
+      </c>
+      <c r="T101">
+        <f>R101*S101</f>
+        <v>-583.851993874595</v>
+      </c>
+      <c r="V101">
+        <f>(C111-C114)*60</f>
+        <v>-1200</v>
+      </c>
+      <c r="W101">
+        <f>COS((H113+H110)/2)</f>
+        <v>0.53604049038068036</v>
+      </c>
+      <c r="X101">
+        <f>V101*W101</f>
+        <v>-643.24858845681638</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="P102">
+        <f>P101/P100</f>
+        <v>6.0914882522873617</v>
+      </c>
+      <c r="T102">
+        <f>T101/T100</f>
+        <v>-6.8012987263294375</v>
+      </c>
+      <c r="X102">
+        <f>X101/X100</f>
+        <v>-2.0732585553220328</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A103" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" s="20"/>
       <c r="E103" s="2" t="s">
         <v>3</v>
       </c>
@@ -1365,61 +1443,72 @@
       <c r="H103" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="104" spans="1:23">
-      <c r="A104" s="11" t="s">
+      <c r="P103">
+        <f>DEGREES(ATAN(P102))</f>
+        <v>80.677279118192374</v>
+      </c>
+      <c r="T103">
+        <f>180+DEGREES(ATAN(T102))</f>
+        <v>98.364311237727648</v>
+      </c>
+      <c r="X103">
+        <f>180+DEGREES(ATAN(X102))</f>
+        <v>115.74952438882954</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A104" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B104" s="11"/>
-      <c r="C104" s="17">
-        <f>DEGREES(ATAN(TAN(RADIANS(C98))*COS(RADIANS(C99-C105))))</f>
-        <v>55</v>
+      <c r="B104" s="21"/>
+      <c r="C104" s="14">
+        <v>60</v>
       </c>
       <c r="E104" t="s">
         <v>5</v>
       </c>
-      <c r="F104" s="17">
+      <c r="F104" s="14">
         <f>C104+D104/60</f>
-        <v>55</v>
-      </c>
-      <c r="G104" s="17">
+        <v>60</v>
+      </c>
+      <c r="G104" s="14">
         <f t="shared" ref="G104:G105" si="13">RADIANS(C104+D104/60)</f>
-        <v>0.95993108859688125</v>
-      </c>
-      <c r="H104" s="16">
+        <v>1.0471975511965976</v>
+      </c>
+      <c r="H104" s="13">
         <f>RADIANS(C104)</f>
-        <v>0.95993108859688125</v>
-      </c>
-    </row>
-    <row r="105" spans="1:23">
-      <c r="A105" s="11" t="s">
+        <v>1.0471975511965976</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A105" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B105" s="11"/>
+      <c r="B105" s="21"/>
       <c r="C105">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="E105" t="s">
         <v>7</v>
       </c>
       <c r="F105">
         <f t="shared" ref="F105" si="14">C105+D105/60</f>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="G105">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="16">
+        <v>-1.2217304763960306</v>
+      </c>
+      <c r="H105" s="13">
         <f>RADIANS(C105)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:23">
-      <c r="A106" s="12" t="s">
+        <v>-1.2217304763960306</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A106" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B106" s="12"/>
+      <c r="B106" s="20"/>
       <c r="E106" s="2" t="s">
         <v>3</v>
       </c>
@@ -1434,45 +1523,45 @@
       </c>
       <c r="J106">
         <f>DEGREES((((H108-H105)*COS((H104+H107)/2))^2+(H107-H104)^2)^(1/2))*60</f>
-        <v>714.16372864074197</v>
+        <v>593.25169464805413</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
-      <c r="A107" s="11" t="s">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A107" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B107" s="11"/>
-      <c r="C107" s="17">
+      <c r="B107" s="21"/>
+      <c r="C107" s="14">
         <f>DEGREES(ATAN(TAN(RADIANS(C98))*COS(RADIANS(C99-C108))))</f>
-        <v>60.170995088911297</v>
+        <v>61.601731622642134</v>
       </c>
       <c r="E107" t="s">
         <v>5</v>
       </c>
-      <c r="F107" s="17">
+      <c r="F107" s="14">
         <f>ROUNDDOWN(C107,0)</f>
-        <v>60</v>
-      </c>
-      <c r="G107" s="17">
+        <v>61</v>
+      </c>
+      <c r="G107" s="14">
         <f>(C107-F107)*60</f>
-        <v>10.259705334677847</v>
-      </c>
-      <c r="H107" s="16">
+        <v>36.103897358528059</v>
+      </c>
+      <c r="H107" s="13">
         <f>RADIANS(C107)</f>
-        <v>1.0501819785028403</v>
+        <v>1.0751530417450144</v>
       </c>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" spans="1:23">
-      <c r="A108" s="11" t="s">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A108" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B108" s="11"/>
+      <c r="B108" s="21"/>
       <c r="C108">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s">
@@ -1480,22 +1569,22 @@
       </c>
       <c r="F108">
         <f t="shared" ref="F108" si="15">C108+D108/60</f>
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="G108">
         <v>0</v>
       </c>
-      <c r="H108" s="16">
+      <c r="H108" s="13">
         <f>RADIANS(C108)</f>
-        <v>0.3490658503988659</v>
+        <v>-0.87266462599716477</v>
       </c>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" spans="1:23">
-      <c r="A109" s="12" t="s">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A109" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B109" s="12"/>
+      <c r="B109" s="20"/>
       <c r="E109" s="2" t="s">
         <v>3</v>
       </c>
@@ -1510,48 +1599,48 @@
       </c>
       <c r="J109">
         <f>DEGREES((((H111-H108)*COS((H107+H110)/2))^2+(H110-H107)^2)^(1/2))*60</f>
-        <v>590.12911812210018</v>
+        <v>590.12911812210052</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
-      <c r="A110" s="11" t="s">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A110" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B110" s="11"/>
-      <c r="C110" s="17">
+      <c r="B110" s="21"/>
+      <c r="C110" s="14">
         <f>DEGREES(ATAN(TAN(RADIANS(C98))*COS(RADIANS(C99-C111))))</f>
-        <v>61.601731622642134</v>
+        <v>60.17099508891129</v>
       </c>
       <c r="E110" t="s">
         <v>5</v>
       </c>
-      <c r="F110" s="22">
+      <c r="F110" s="19">
         <f>ROUNDDOWN(C110,0)</f>
-        <v>61</v>
-      </c>
-      <c r="G110" s="17">
+        <v>60</v>
+      </c>
+      <c r="G110" s="14">
         <f>(C110-F110)*60</f>
-        <v>36.103897358528059</v>
-      </c>
-      <c r="H110" s="16">
+        <v>10.25970533467742</v>
+      </c>
+      <c r="H110" s="13">
         <f>RADIANS(C110)</f>
-        <v>1.0751530417450144</v>
+        <v>1.0501819785028401</v>
       </c>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" spans="1:23">
-      <c r="A111" s="11" t="s">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A111" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B111" s="11"/>
+      <c r="B111" s="21"/>
       <c r="C111">
-        <v>40</v>
+        <v>-30</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F111">
         <v>40</v>
@@ -1559,17 +1648,17 @@
       <c r="G111">
         <v>0</v>
       </c>
-      <c r="H111" s="16">
+      <c r="H111" s="13">
         <f>RADIANS(C111)</f>
-        <v>0.69813170079773179</v>
+        <v>-0.52359877559829882</v>
       </c>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" spans="1:23">
-      <c r="A112" s="12" t="s">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A112" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="12"/>
+      <c r="B112" s="20"/>
       <c r="E112" s="2" t="s">
         <v>3</v>
       </c>
@@ -1584,113 +1673,113 @@
       </c>
       <c r="J112">
         <f>DEGREES((((H114-H111)*COS((H110+H113)/2))^2+(H113-H110)^2)^(1/2))*60</f>
-        <v>593.25169464805447</v>
+        <v>714.16372864074265</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
-      <c r="A113" s="11" t="s">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B113" s="11"/>
-      <c r="C113" s="17">
+      <c r="B113" s="21"/>
+      <c r="C113" s="14">
         <f>DEGREES(ATAN(TAN(RADIANS(C98))*COS(RADIANS(C99-C114))))</f>
-        <v>59.999999999999986</v>
+        <v>54.999999999999972</v>
       </c>
       <c r="E113" t="s">
         <v>5</v>
       </c>
-      <c r="F113" s="17">
+      <c r="F113" s="14">
         <f>ROUNDDOWN(C113,0)</f>
-        <v>60</v>
-      </c>
-      <c r="G113" s="17">
+        <v>55</v>
+      </c>
+      <c r="G113" s="14">
         <f>ROUNDDOWN((C113-F113)*60,0)</f>
         <v>0</v>
       </c>
-      <c r="H113" s="16">
+      <c r="H113" s="13">
         <f>RADIANS(C113+D113/60)</f>
-        <v>1.0471975511965974</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" s="11" t="s">
+        <v>0.95993108859688081</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B114" s="11"/>
+      <c r="B114" s="21"/>
       <c r="C114">
-        <v>60</v>
+        <v>-10</v>
       </c>
       <c r="D114" s="9"/>
       <c r="E114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F114">
-        <f t="shared" ref="F113:F114" si="16">C114+D114/60</f>
-        <v>60</v>
+        <f t="shared" ref="F114" si="16">C114+D114/60</f>
+        <v>-10</v>
       </c>
       <c r="G114">
         <v>0</v>
       </c>
-      <c r="H114" s="16">
+      <c r="H114" s="13">
         <f>RADIANS(C114+D114/60)</f>
-        <v>1.0471975511965976</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
+        <v>-0.17453292519943295</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="J115">
         <f>SUM(J106:J112)</f>
-        <v>1897.5445414108967</v>
+        <v>1897.5445414108972</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="8"/>
     </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="21"/>
+      <c r="B130" s="21"/>
       <c r="C130" s="4"/>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C131" s="4"/>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="4"/>
     </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="21"/>
+      <c r="B133" s="21"/>
       <c r="C133" s="5"/>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C134" s="5"/>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="4"/>
     </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="21"/>
+      <c r="B136" s="21"/>
       <c r="C136" s="4"/>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C137" s="4"/>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C141" s="4"/>
     </row>
-    <row r="1048576" spans="6:37">
+    <row r="1048576" spans="6:37" x14ac:dyDescent="0.25">
       <c r="F1048576" s="1"/>
       <c r="G1048576" s="1"/>
       <c r="H1048576" s="1"/>
@@ -1728,6 +1817,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A91:B91"/>
     <mergeCell ref="A112:B112"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A89:B89"/>
@@ -1744,35 +1862,6 @@
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
